--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430468</v>
+        <v>121430846</v>
       </c>
       <c r="B2" t="n">
-        <v>98115</v>
+        <v>97998</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488211</v>
+        <v>488336</v>
       </c>
       <c r="R2" t="n">
-        <v>6656672</v>
+        <v>6656637</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430212</v>
+        <v>121430468</v>
       </c>
       <c r="B3" t="n">
-        <v>98104</v>
+        <v>98115</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488332</v>
+        <v>488211</v>
       </c>
       <c r="R3" t="n">
-        <v>6656638</v>
+        <v>6656672</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -989,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430464</v>
+        <v>121430212</v>
       </c>
       <c r="B5" t="n">
-        <v>98115</v>
+        <v>98104</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,26 +1005,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488046</v>
+        <v>488332</v>
       </c>
       <c r="R5" t="n">
-        <v>6656667</v>
+        <v>6656638</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430846</v>
+        <v>121430464</v>
       </c>
       <c r="B6" t="n">
-        <v>97998</v>
+        <v>98115</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488336</v>
+        <v>488046</v>
       </c>
       <c r="R6" t="n">
-        <v>6656637</v>
+        <v>6656667</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430846</v>
       </c>
       <c r="B2" t="n">
-        <v>97998</v>
+        <v>98011</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121430468</v>
       </c>
       <c r="B3" t="n">
-        <v>98115</v>
+        <v>98128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -883,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430851</v>
+        <v>121430464</v>
       </c>
       <c r="B4" t="n">
-        <v>97998</v>
+        <v>98128</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,26 +899,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488045</v>
+        <v>488046</v>
       </c>
       <c r="R4" t="n">
-        <v>6656666</v>
+        <v>6656667</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -992,7 +992,7 @@
         <v>121430212</v>
       </c>
       <c r="B5" t="n">
-        <v>98104</v>
+        <v>98117</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430464</v>
+        <v>121430851</v>
       </c>
       <c r="B6" t="n">
-        <v>98115</v>
+        <v>98011</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488046</v>
+        <v>488045</v>
       </c>
       <c r="R6" t="n">
-        <v>6656667</v>
+        <v>6656666</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430846</v>
+        <v>121430851</v>
       </c>
       <c r="B2" t="n">
-        <v>98011</v>
+        <v>98012</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488336</v>
+        <v>488045</v>
       </c>
       <c r="R2" t="n">
-        <v>6656637</v>
+        <v>6656666</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Lisa Stridh, Emma Karlsson, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430468</v>
+        <v>121430464</v>
       </c>
       <c r="B3" t="n">
-        <v>98128</v>
+        <v>98129</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -814,17 +814,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488211</v>
+        <v>488046</v>
       </c>
       <c r="R3" t="n">
-        <v>6656672</v>
+        <v>6656667</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,17 +880,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430464</v>
+        <v>121430846</v>
       </c>
       <c r="B4" t="n">
-        <v>98128</v>
+        <v>98012</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,26 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488046</v>
+        <v>488336</v>
       </c>
       <c r="R4" t="n">
-        <v>6656667</v>
+        <v>6656637</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,7 +986,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -992,7 +996,7 @@
         <v>121430212</v>
       </c>
       <c r="B5" t="n">
-        <v>98117</v>
+        <v>98118</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,17 +1092,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430851</v>
+        <v>121430468</v>
       </c>
       <c r="B6" t="n">
-        <v>98011</v>
+        <v>98129</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488045</v>
+        <v>488211</v>
       </c>
       <c r="R6" t="n">
-        <v>6656666</v>
+        <v>6656672</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430851</v>
+        <v>121430468</v>
       </c>
       <c r="B2" t="n">
-        <v>98012</v>
+        <v>98132</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488045</v>
+        <v>488211</v>
       </c>
       <c r="R2" t="n">
-        <v>6656666</v>
+        <v>6656672</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430464</v>
+        <v>121430846</v>
       </c>
       <c r="B3" t="n">
-        <v>98129</v>
+        <v>98015</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488046</v>
+        <v>488336</v>
       </c>
       <c r="R3" t="n">
-        <v>6656667</v>
+        <v>6656637</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,10 +883,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430846</v>
+        <v>121430212</v>
       </c>
       <c r="B4" t="n">
-        <v>98012</v>
+        <v>98121</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +899,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488336</v>
+        <v>488332</v>
       </c>
       <c r="R4" t="n">
-        <v>6656637</v>
+        <v>6656638</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,10 +989,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430212</v>
+        <v>121430851</v>
       </c>
       <c r="B5" t="n">
-        <v>98118</v>
+        <v>98015</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1005,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488332</v>
+        <v>488045</v>
       </c>
       <c r="R5" t="n">
-        <v>6656638</v>
+        <v>6656666</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,17 +1088,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430468</v>
+        <v>121430464</v>
       </c>
       <c r="B6" t="n">
-        <v>98129</v>
+        <v>98132</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1132,17 +1128,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488211</v>
+        <v>488046</v>
       </c>
       <c r="R6" t="n">
-        <v>6656672</v>
+        <v>6656667</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430468</v>
+        <v>121430464</v>
       </c>
       <c r="B2" t="n">
         <v>98132</v>
@@ -708,17 +708,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488211</v>
+        <v>488046</v>
       </c>
       <c r="R2" t="n">
-        <v>6656672</v>
+        <v>6656667</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Stridh, Emma Karlsson, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430846</v>
+        <v>121430468</v>
       </c>
       <c r="B3" t="n">
-        <v>98015</v>
+        <v>98132</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,38 +797,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488336</v>
+        <v>488211</v>
       </c>
       <c r="R3" t="n">
-        <v>6656637</v>
+        <v>6656672</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +876,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -982,7 +982,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1095,10 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430464</v>
+        <v>121430846</v>
       </c>
       <c r="B6" t="n">
-        <v>98132</v>
+        <v>98015</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,26 +1111,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488046</v>
+        <v>488336</v>
       </c>
       <c r="R6" t="n">
-        <v>6656667</v>
+        <v>6656637</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121430464</v>
       </c>
       <c r="B2" t="n">
-        <v>98132</v>
+        <v>98138</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -784,7 +784,7 @@
         <v>121430468</v>
       </c>
       <c r="B3" t="n">
-        <v>98132</v>
+        <v>98138</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -886,7 +886,7 @@
         <v>121430212</v>
       </c>
       <c r="B4" t="n">
-        <v>98121</v>
+        <v>98127</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>121430851</v>
       </c>
       <c r="B5" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1098,7 +1098,7 @@
         <v>121430846</v>
       </c>
       <c r="B6" t="n">
-        <v>98015</v>
+        <v>98021</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430464</v>
+        <v>121430212</v>
       </c>
       <c r="B2" t="n">
-        <v>98138</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488046</v>
+        <v>488332</v>
       </c>
       <c r="R2" t="n">
-        <v>6656667</v>
+        <v>6656638</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,10 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430468</v>
+        <v>121430851</v>
       </c>
       <c r="B3" t="n">
-        <v>98138</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,34 +797,38 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488211</v>
+        <v>488045</v>
       </c>
       <c r="R3" t="n">
-        <v>6656672</v>
+        <v>6656666</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -883,10 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430212</v>
+        <v>121430464</v>
       </c>
       <c r="B4" t="n">
-        <v>98127</v>
+        <v>98139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,26 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488332</v>
+        <v>488046</v>
       </c>
       <c r="R4" t="n">
-        <v>6656638</v>
+        <v>6656667</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430851</v>
+        <v>121430468</v>
       </c>
       <c r="B5" t="n">
-        <v>98021</v>
+        <v>98139</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488045</v>
+        <v>488211</v>
       </c>
       <c r="R5" t="n">
-        <v>6656666</v>
+        <v>6656672</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1098,7 +1098,7 @@
         <v>121430846</v>
       </c>
       <c r="B6" t="n">
-        <v>98021</v>
+        <v>98022</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430212</v>
+        <v>121430468</v>
       </c>
       <c r="B2" t="n">
-        <v>98128</v>
+        <v>98139</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,38 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488332</v>
+        <v>488211</v>
       </c>
       <c r="R2" t="n">
-        <v>6656638</v>
+        <v>6656672</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,17 +770,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430851</v>
+        <v>121430212</v>
       </c>
       <c r="B3" t="n">
-        <v>98022</v>
+        <v>98128</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -797,26 +793,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +821,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488045</v>
+        <v>488332</v>
       </c>
       <c r="R3" t="n">
-        <v>6656666</v>
+        <v>6656638</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,17 +876,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430464</v>
+        <v>121430846</v>
       </c>
       <c r="B4" t="n">
-        <v>98139</v>
+        <v>98022</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,26 +899,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488046</v>
+        <v>488336</v>
       </c>
       <c r="R4" t="n">
-        <v>6656667</v>
+        <v>6656637</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -993,7 +989,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430468</v>
+        <v>121430464</v>
       </c>
       <c r="B5" t="n">
         <v>98139</v>
@@ -1026,17 +1022,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488211</v>
+        <v>488046</v>
       </c>
       <c r="R5" t="n">
-        <v>6656672</v>
+        <v>6656667</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,14 +1088,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430846</v>
+        <v>121430851</v>
       </c>
       <c r="B6" t="n">
         <v>98022</v>
@@ -1130,7 +1130,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1139,10 +1139,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488336</v>
+        <v>488045</v>
       </c>
       <c r="R6" t="n">
-        <v>6656637</v>
+        <v>6656666</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430468</v>
+        <v>121430464</v>
       </c>
       <c r="B2" t="n">
         <v>98139</v>
@@ -708,17 +708,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr"/>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488211</v>
+        <v>488046</v>
       </c>
       <c r="R2" t="n">
-        <v>6656672</v>
+        <v>6656667</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,17 +774,17 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430212</v>
+        <v>121430851</v>
       </c>
       <c r="B3" t="n">
-        <v>98128</v>
+        <v>98022</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,26 +797,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488332</v>
+        <v>488045</v>
       </c>
       <c r="R3" t="n">
-        <v>6656638</v>
+        <v>6656666</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,7 +880,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -989,10 +993,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430464</v>
+        <v>121430212</v>
       </c>
       <c r="B5" t="n">
-        <v>98139</v>
+        <v>98128</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,26 +1009,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1033,10 +1037,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488046</v>
+        <v>488332</v>
       </c>
       <c r="R5" t="n">
-        <v>6656667</v>
+        <v>6656638</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1095,10 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430851</v>
+        <v>121430468</v>
       </c>
       <c r="B6" t="n">
-        <v>98022</v>
+        <v>98139</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1111,38 +1115,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488045</v>
+        <v>488211</v>
       </c>
       <c r="R6" t="n">
-        <v>6656666</v>
+        <v>6656672</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430464</v>
+        <v>121430212</v>
       </c>
       <c r="B2" t="n">
-        <v>98139</v>
+        <v>98128</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,26 +691,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488046</v>
+        <v>488332</v>
       </c>
       <c r="R2" t="n">
-        <v>6656667</v>
+        <v>6656638</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -774,14 +774,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430851</v>
+        <v>121430846</v>
       </c>
       <c r="B3" t="n">
         <v>98022</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488045</v>
+        <v>488336</v>
       </c>
       <c r="R3" t="n">
-        <v>6656666</v>
+        <v>6656637</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,17 +880,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430846</v>
+        <v>121430468</v>
       </c>
       <c r="B4" t="n">
-        <v>98022</v>
+        <v>98139</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -903,38 +903,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219874</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488336</v>
+        <v>488211</v>
       </c>
       <c r="R4" t="n">
-        <v>6656637</v>
+        <v>6656672</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,17 +982,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430212</v>
+        <v>121430851</v>
       </c>
       <c r="B5" t="n">
-        <v>98128</v>
+        <v>98022</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1009,26 +1005,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1037,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488332</v>
+        <v>488045</v>
       </c>
       <c r="R5" t="n">
-        <v>6656638</v>
+        <v>6656666</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1092,14 +1088,14 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121430468</v>
+        <v>121430464</v>
       </c>
       <c r="B6" t="n">
         <v>98139</v>
@@ -1132,17 +1128,21 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>488211</v>
+        <v>488046</v>
       </c>
       <c r="R6" t="n">
-        <v>6656672</v>
+        <v>6656667</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121430468</v>
+        <v>121430846</v>
       </c>
       <c r="B2" t="n">
-        <v>98147</v>
+        <v>98030</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,38 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219874</v>
+        <v>219790</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>488211</v>
+        <v>488336</v>
       </c>
       <c r="R2" t="n">
-        <v>6656672</v>
+        <v>6656637</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -770,14 +774,14 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430846</v>
+        <v>121430851</v>
       </c>
       <c r="B3" t="n">
         <v>98030</v>
@@ -812,7 +816,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -821,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488336</v>
+        <v>488045</v>
       </c>
       <c r="R3" t="n">
-        <v>6656637</v>
+        <v>6656666</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -876,17 +880,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Emma Karlsson, Lisa Stridh, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430851</v>
+        <v>121430212</v>
       </c>
       <c r="B4" t="n">
-        <v>98030</v>
+        <v>98136</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -899,26 +903,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>219847</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -927,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488045</v>
+        <v>488332</v>
       </c>
       <c r="R4" t="n">
-        <v>6656666</v>
+        <v>6656638</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -982,17 +986,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Stridh, Emma Karlsson, Anna-Lotta Hellqvist</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430212</v>
+        <v>121430468</v>
       </c>
       <c r="B5" t="n">
-        <v>98136</v>
+        <v>98147</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1005,38 +1009,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219847</v>
+        <v>219874</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Nattviol</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Platanthera bifolia</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488332</v>
+        <v>488211</v>
       </c>
       <c r="R5" t="n">
-        <v>6656638</v>
+        <v>6656672</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>121430846</v>
       </c>
       <c r="B2" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121430851</v>
+        <v>121430849</v>
       </c>
       <c r="B3" t="n">
-        <v>98030</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -814,21 +804,17 @@
           <t>(L.) Soó</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>488045</v>
+        <v>488038</v>
       </c>
       <c r="R3" t="n">
-        <v>6656666</v>
+        <v>6656711</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,15 +873,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121430212</v>
+        <v>121430851</v>
       </c>
       <c r="B4" t="n">
-        <v>98136</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,26 +884,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219847</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -931,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>488332</v>
+        <v>488045</v>
       </c>
       <c r="R4" t="n">
-        <v>6656638</v>
+        <v>6656666</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,22 +967,17 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121430468</v>
+        <v>121430212</v>
       </c>
       <c r="B5" t="n">
-        <v>98147</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99142</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,34 +985,38 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219874</v>
+        <v>219847</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nattviol</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Platanthera bifolia</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Yxsjöberg, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>488211</v>
+        <v>488332</v>
       </c>
       <c r="R5" t="n">
-        <v>6656672</v>
+        <v>6656638</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1088,7 +1068,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+          <t>Anna-Lotta Hellqvist, Lisa Stridh, Emma Karlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1098,12 +1078,7 @@
         <v>121430464</v>
       </c>
       <c r="B6" t="n">
-        <v>98147</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99153</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,6 +1173,301 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>121430467</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Yxsjöberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>488024</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6656703</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>121430468</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99153</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219874</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Nattviol</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Yxsjöberg, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>488211</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6656672</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-17</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Anna-Lotta Hellqvist, Emma Karlsson, Lisa Stridh</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>6178630</v>
+      </c>
+      <c r="B9" t="n">
+        <v>106417</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>224210</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Tidig fältgentiana</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Gentianella campestris var. suecica</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Froel.) Dostál</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Yxsjöberg, strax O om avtag mot Älvhöjden, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>488166</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6656698</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2003-06-30</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2003-06-30</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 43996-2021 artfynd.xlsx
+++ b/artfynd/A 43996-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430846</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -870,6 +880,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -971,6 +986,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430851</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430212</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1173,6 +1198,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1270,6 +1300,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430467</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1367,6 +1402,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121430468</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1468,8 +1508,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6178630</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>